--- a/report_scripts/Brockway Paul/aggregation_mapping.xlsx
+++ b/report_scripts/Brockway Paul/aggregation_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leeds365-my.sharepoint.com/personal/earpebr_leeds_ac_uk/Documents/PFU 1960-2020 database research/InputData/v3.0a1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkh2/github/PFUPipeline2/report_scripts/Brockway Paul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{11B3DC84-8A9C-0749-A7A0-D0517496FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F4FC2EE-B299-49F0-8726-EA9DF1F798E5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41476E5-6521-7D4A-AF0E-3E2BBB901F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="16440" tabRatio="781" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="region_aggregation" sheetId="22" r:id="rId1"/>
@@ -25,9 +25,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">continent_aggregation!$B$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ef.iea_product_aggregation!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ef_product_aggregation!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">ef_sector_aggregation!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ef.iea_product_aggregation!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">eu_product_aggregation!$A$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">region_aggregation!$B$1:$B$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">world_aggregation!$B$1:$B$1</definedName>
@@ -2385,9 +2385,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2398,6 +2395,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3312,14 +3312,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC20FE3-2C61-DD4B-AC4F-4EDDF1FDEE75}">
   <dimension ref="A1:B260"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.42578125" style="1"/>
+    <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>163</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>22</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>40</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>27</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>33</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>30</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>11</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>29</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>54</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>55</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>56</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>57</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>58</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>59</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>60</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>61</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>62</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>63</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>64</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>65</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>66</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>67</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>68</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>56</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>58</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>57</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>69</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>70</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>71</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>72</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>73</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>74</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>76</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>77</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>78</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>79</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>80</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>81</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
         <v>59</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
         <v>82</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>83</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
         <v>60</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
         <v>173</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
         <v>84</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>85</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
         <v>4</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
         <v>61</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
         <v>87</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
         <v>7</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
         <v>88</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
         <v>62</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
         <v>89</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
         <v>8</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
         <v>9</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
         <v>63</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
         <v>90</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
         <v>64</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
         <v>91</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
         <v>92</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
         <v>65</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
         <v>66</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
         <v>93</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
         <v>16</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
         <v>67</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
         <v>94</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
         <v>17</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
         <v>68</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
         <v>95</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
         <v>96</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
         <v>97</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
         <v>98</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
         <v>99</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
         <v>100</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
         <v>101</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
         <v>102</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
         <v>103</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
         <v>104</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
         <v>105</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
         <v>106</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
         <v>107</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
         <v>108</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
         <v>109</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
         <v>110</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
         <v>111</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
         <v>112</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
         <v>113</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
         <v>114</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
         <v>115</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
         <v>116</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
         <v>117</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
         <v>118</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
         <v>119</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
         <v>120</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
         <v>121</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
         <v>122</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
         <v>123</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
         <v>124</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
         <v>125</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
         <v>126</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
         <v>127</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
         <v>128</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
         <v>129</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
         <v>130</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
         <v>131</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
         <v>132</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
         <v>133</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A160" s="1" t="s">
         <v>134</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
         <v>135</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
         <v>136</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
         <v>137</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
         <v>138</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
         <v>139</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
         <v>37</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
         <v>38</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
         <v>39</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
         <v>22</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
         <v>40</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
         <v>27</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
         <v>41</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A175" s="1" t="s">
         <v>6</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
         <v>42</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
         <v>43</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
         <v>33</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
         <v>44</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
         <v>45</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
         <v>140</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
         <v>46</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
         <v>47</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
         <v>11</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
         <v>10</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
         <v>48</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
         <v>23</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
         <v>49</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
         <v>12</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A190" s="18" t="s">
         <v>24</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
         <v>141</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
         <v>51</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
         <v>52</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
         <v>53</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
         <v>13</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A197" s="18" t="s">
         <v>25</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
         <v>29</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
         <v>15</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
         <v>54</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
         <v>55</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
         <v>142</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
         <v>18</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
         <v>143</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A205" s="18" t="s">
         <v>163</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
         <v>87</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
         <v>8</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
         <v>9</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
         <v>13</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
         <v>16</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
         <v>88</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
         <v>95</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
         <v>97</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
         <v>34</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
         <v>43</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
         <v>33</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
         <v>47</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
         <v>89</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
         <v>143</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
         <v>36</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
         <v>84</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
         <v>37</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
         <v>38</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
         <v>34</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
         <v>69</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
         <v>70</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
         <v>71</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
         <v>27</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A231" s="1" t="s">
         <v>41</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A232" s="1" t="s">
         <v>6</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A233" s="1" t="s">
         <v>42</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A234" s="1" t="s">
         <v>43</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A235" s="1" t="s">
         <v>33</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A236" s="1" t="s">
         <v>44</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A237" s="1" t="s">
         <v>45</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
         <v>140</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A239" s="1" t="s">
         <v>46</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A240" s="1" t="s">
         <v>99</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A241" s="1" t="s">
         <v>47</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A242" s="1" t="s">
         <v>89</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A243" s="1" t="s">
         <v>11</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A244" s="1" t="s">
         <v>10</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A245" s="1" t="s">
         <v>48</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A246" s="1" t="s">
         <v>35</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
         <v>50</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
         <v>85</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
         <v>141</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
         <v>51</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
         <v>52</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
         <v>29</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
         <v>15</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
         <v>92</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
         <v>54</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
         <v>55</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
         <v>142</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A258" s="1" t="s">
         <v>94</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
         <v>143</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
         <v>36</v>
       </c>
@@ -5409,14 +5409,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B160"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.42578125" style="1"/>
+    <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>111</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>119</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>112</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>114</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>113</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>108</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>115</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>145</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>116</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>117</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>118</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>146</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>120</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>147</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>121</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>124</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>122</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>125</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>123</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>126</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>127</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>148</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>149</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>128</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>131</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>129</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>150</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>132</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>134</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>135</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>133</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>136</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>130</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>137</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>138</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>2</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>4</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>86</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>61</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>87</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>152</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>89</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>9</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>153</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>92</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>154</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>93</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>64</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>90</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>91</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>155</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>95</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>65</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>156</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>67</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>16</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>17</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>94</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>157</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>158</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>160</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>139</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>37</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>38</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>39</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>20</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>142</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>40</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>27</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>33</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>41</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>54</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>6</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>42</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>43</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>143</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
         <v>162</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
         <v>44</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>22</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
         <v>45</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
         <v>46</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
         <v>140</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>47</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
         <v>10</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
         <v>48</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
         <v>11</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
         <v>23</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
         <v>49</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
         <v>24</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
         <v>50</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
         <v>141</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
         <v>51</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
         <v>52</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
         <v>53</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
         <v>13</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
         <v>14</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
         <v>29</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
         <v>15</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
         <v>55</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
         <v>18</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
         <v>163</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
         <v>26</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
         <v>107</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
         <v>96</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
         <v>97</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
         <v>98</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
         <v>99</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
         <v>100</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
         <v>101</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
         <v>102</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
         <v>103</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
         <v>104</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
         <v>105</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
         <v>106</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
         <v>165</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
         <v>34</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
         <v>35</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
         <v>36</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
         <v>85</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
         <v>56</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
         <v>58</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
         <v>57</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
         <v>69</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
         <v>70</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
         <v>71</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
         <v>72</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
         <v>169</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
         <v>170</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
         <v>73</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
         <v>75</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
         <v>76</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
         <v>78</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
         <v>77</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
         <v>79</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
         <v>80</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
         <v>171</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
         <v>81</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
         <v>82</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
         <v>59</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
         <v>74</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
         <v>172</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
         <v>83</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
         <v>60</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
         <v>173</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B160" s="1"/>
     </row>
   </sheetData>
@@ -6706,14 +6706,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.42578125" style="1"/>
+    <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>144</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>151</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>161</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>166</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>167</v>
       </c>
@@ -6769,7 +6769,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>168</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>159</v>
       </c>
@@ -6793,15 +6793,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B117"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.42578125" style="14"/>
+    <col min="1" max="1" width="26.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.5" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>175</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
         <v>177</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="15" t="s">
         <v>179</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="15" t="s">
         <v>180</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>181</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
         <v>183</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
         <v>184</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>185</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
         <v>186</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="15" t="s">
         <v>187</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
         <v>188</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
         <v>189</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
         <v>190</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="15" t="s">
         <v>191</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="15" t="s">
         <v>193</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="15" t="s">
         <v>194</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="15" t="s">
         <v>196</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="15" t="s">
         <v>197</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="15" t="s">
         <v>198</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
         <v>200</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
         <v>201</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
         <v>202</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
         <v>203</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
         <v>205</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
         <v>206</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="15" t="s">
         <v>207</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="15" t="s">
         <v>208</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="15" t="s">
         <v>209</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
         <v>210</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
         <v>211</v>
       </c>
@@ -7049,268 +7049,13 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>213</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="14"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="14"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35" s="14"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B36" s="14"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" s="14"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38" s="14"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39" s="14"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40" s="14"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41" s="14"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42" s="14"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43" s="14"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B44" s="14"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B45" s="14"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B46" s="14"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B47" s="14"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B48" s="14"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" s="14"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" s="14"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51" s="14"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52" s="14"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53" s="14"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54" s="14"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55" s="14"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56" s="14"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57" s="14"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B58" s="14"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59" s="14"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60" s="14"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61" s="14"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62" s="14"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63" s="14"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64" s="14"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65" s="14"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66" s="14"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67" s="14"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68" s="14"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69" s="14"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70" s="14"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71" s="14"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72" s="14"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73" s="14"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74" s="14"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="14"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76" s="14"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77" s="14"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78" s="14"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79" s="14"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80" s="14"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81" s="14"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82" s="14"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83" s="14"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84" s="14"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85" s="14"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86" s="14"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87" s="14"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88" s="14"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89" s="14"/>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90" s="14"/>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91" s="14"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92" s="14"/>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93" s="14"/>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94" s="14"/>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95" s="14"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96" s="14"/>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97" s="14"/>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98" s="14"/>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99" s="14"/>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100" s="14"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101" s="14"/>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102" s="14"/>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103" s="14"/>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104" s="14"/>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105" s="14"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B106" s="14"/>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" s="14"/>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" s="14"/>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B109" s="14"/>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B110" s="14"/>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B111" s="14"/>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B112" s="14"/>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B113" s="14"/>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B114" s="14"/>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B115" s="14"/>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B116" s="14"/>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B117" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
@@ -7322,14 +7067,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7338,7 +7083,7 @@
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>214</v>
       </c>
@@ -7346,7 +7091,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>216</v>
       </c>
@@ -7354,7 +7099,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>217</v>
       </c>
@@ -7362,7 +7107,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>218</v>
       </c>
@@ -7370,7 +7115,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>219</v>
       </c>
@@ -7378,7 +7123,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>220</v>
       </c>
@@ -7386,7 +7131,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>221</v>
       </c>
@@ -7394,7 +7139,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>222</v>
       </c>
@@ -7402,7 +7147,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>223</v>
       </c>
@@ -7410,7 +7155,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>224</v>
       </c>
@@ -7418,7 +7163,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>225</v>
       </c>
@@ -7426,7 +7171,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>226</v>
       </c>
@@ -7434,7 +7179,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>227</v>
       </c>
@@ -7442,7 +7187,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>228</v>
       </c>
@@ -7450,7 +7195,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>229</v>
       </c>
@@ -7458,7 +7203,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>230</v>
       </c>
@@ -7466,7 +7211,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
         <v>231</v>
       </c>
@@ -7474,7 +7219,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
         <v>233</v>
       </c>
@@ -7482,7 +7227,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="9" t="s">
         <v>234</v>
       </c>
@@ -7490,7 +7235,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>236</v>
       </c>
@@ -7498,7 +7243,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="9" t="s">
         <v>237</v>
       </c>
@@ -7506,7 +7251,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="9" t="s">
         <v>239</v>
       </c>
@@ -7514,7 +7259,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="9" t="s">
         <v>240</v>
       </c>
@@ -7522,7 +7267,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="9" t="s">
         <v>241</v>
       </c>
@@ -7530,7 +7275,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="9" t="s">
         <v>242</v>
       </c>
@@ -7538,7 +7283,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="9" t="s">
         <v>243</v>
       </c>
@@ -7546,7 +7291,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>244</v>
       </c>
@@ -7554,7 +7299,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>246</v>
       </c>
@@ -7562,7 +7307,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>247</v>
       </c>
@@ -7570,7 +7315,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>248</v>
       </c>
@@ -7578,7 +7323,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>249</v>
       </c>
@@ -7586,7 +7331,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>250</v>
       </c>
@@ -7594,7 +7339,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>251</v>
       </c>
@@ -7602,7 +7347,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>252</v>
       </c>
@@ -7610,7 +7355,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>253</v>
       </c>
@@ -7618,7 +7363,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>254</v>
       </c>
@@ -7626,7 +7371,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>255</v>
       </c>
@@ -7634,7 +7379,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>256</v>
       </c>
@@ -7642,7 +7387,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>257</v>
       </c>
@@ -7650,7 +7395,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>258</v>
       </c>
@@ -7658,7 +7403,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>259</v>
       </c>
@@ -7666,7 +7411,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>260</v>
       </c>
@@ -7674,7 +7419,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>261</v>
       </c>
@@ -7682,7 +7427,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>262</v>
       </c>
@@ -7690,7 +7435,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
         <v>264</v>
       </c>
@@ -7698,7 +7443,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
         <v>265</v>
       </c>
@@ -7706,7 +7451,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
         <v>266</v>
       </c>
@@ -7714,7 +7459,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
         <v>267</v>
       </c>
@@ -7722,7 +7467,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
         <v>268</v>
       </c>
@@ -7730,7 +7475,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
         <v>269</v>
       </c>
@@ -7738,7 +7483,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
         <v>270</v>
       </c>
@@ -7746,7 +7491,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
         <v>271</v>
       </c>
@@ -7754,7 +7499,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
         <v>272</v>
       </c>
@@ -7762,7 +7507,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
         <v>273</v>
       </c>
@@ -7770,7 +7515,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
         <v>274</v>
       </c>
@@ -7779,7 +7524,7 @@
       </c>
       <c r="C56" s="10"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
         <v>276</v>
       </c>
@@ -7788,7 +7533,7 @@
       </c>
       <c r="C57" s="10"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
         <v>277</v>
       </c>
@@ -7797,7 +7542,7 @@
       </c>
       <c r="C58" s="10"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
         <v>278</v>
       </c>
@@ -7806,7 +7551,7 @@
       </c>
       <c r="C59" s="10"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
         <v>279</v>
       </c>
@@ -7814,7 +7559,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
         <v>280</v>
       </c>
@@ -7823,7 +7568,7 @@
       </c>
       <c r="C61" s="10"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
         <v>281</v>
       </c>
@@ -7831,7 +7576,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
         <v>282</v>
       </c>
@@ -7840,7 +7585,7 @@
       </c>
       <c r="C63" s="10"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
         <v>283</v>
       </c>
@@ -7849,7 +7594,7 @@
       </c>
       <c r="C64" s="10"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
         <v>284</v>
       </c>
@@ -7858,7 +7603,7 @@
       </c>
       <c r="C65" s="10"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
         <v>285</v>
       </c>
@@ -7866,7 +7611,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
         <v>286</v>
       </c>
@@ -7874,7 +7619,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68" s="15" t="s">
         <v>287</v>
       </c>
@@ -7882,7 +7627,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69" s="15" t="s">
         <v>288</v>
       </c>
@@ -7899,14 +7644,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7915,7 +7660,7 @@
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>214</v>
       </c>
@@ -7923,7 +7668,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>216</v>
       </c>
@@ -7931,7 +7676,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>217</v>
       </c>
@@ -7939,7 +7684,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>218</v>
       </c>
@@ -7947,7 +7692,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>219</v>
       </c>
@@ -7955,7 +7700,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>220</v>
       </c>
@@ -7963,7 +7708,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>221</v>
       </c>
@@ -7971,7 +7716,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>222</v>
       </c>
@@ -7979,7 +7724,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>223</v>
       </c>
@@ -7987,7 +7732,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>224</v>
       </c>
@@ -7995,7 +7740,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>225</v>
       </c>
@@ -8003,7 +7748,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>226</v>
       </c>
@@ -8011,7 +7756,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>227</v>
       </c>
@@ -8019,7 +7764,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>228</v>
       </c>
@@ -8027,7 +7772,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>229</v>
       </c>
@@ -8035,7 +7780,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>230</v>
       </c>
@@ -8043,7 +7788,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
         <v>231</v>
       </c>
@@ -8051,7 +7796,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
         <v>233</v>
       </c>
@@ -8059,7 +7804,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
         <v>234</v>
       </c>
@@ -8067,7 +7812,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>236</v>
       </c>
@@ -8075,7 +7820,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>237</v>
       </c>
@@ -8083,7 +7828,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>239</v>
       </c>
@@ -8091,7 +7836,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>240</v>
       </c>
@@ -8099,7 +7844,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
         <v>241</v>
       </c>
@@ -8107,7 +7852,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>242</v>
       </c>
@@ -8115,7 +7860,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>243</v>
       </c>
@@ -8123,7 +7868,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>244</v>
       </c>
@@ -8131,7 +7876,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>246</v>
       </c>
@@ -8139,7 +7884,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>247</v>
       </c>
@@ -8147,7 +7892,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>248</v>
       </c>
@@ -8155,7 +7900,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>249</v>
       </c>
@@ -8163,7 +7908,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>250</v>
       </c>
@@ -8171,7 +7916,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>251</v>
       </c>
@@ -8179,7 +7924,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>252</v>
       </c>
@@ -8187,7 +7932,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>253</v>
       </c>
@@ -8195,7 +7940,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>254</v>
       </c>
@@ -8203,7 +7948,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>255</v>
       </c>
@@ -8211,7 +7956,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>256</v>
       </c>
@@ -8219,7 +7964,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
         <v>257</v>
       </c>
@@ -8227,7 +7972,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
         <v>258</v>
       </c>
@@ -8235,7 +7980,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
         <v>259</v>
       </c>
@@ -8243,7 +7988,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
         <v>260</v>
       </c>
@@ -8251,7 +7996,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
         <v>261</v>
       </c>
@@ -8259,7 +8004,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>262</v>
       </c>
@@ -8267,7 +8012,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
         <v>264</v>
       </c>
@@ -8275,7 +8020,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
         <v>265</v>
       </c>
@@ -8283,7 +8028,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
         <v>266</v>
       </c>
@@ -8291,7 +8036,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
         <v>267</v>
       </c>
@@ -8299,7 +8044,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
         <v>268</v>
       </c>
@@ -8307,7 +8052,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
         <v>269</v>
       </c>
@@ -8315,7 +8060,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
         <v>270</v>
       </c>
@@ -8323,7 +8068,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
         <v>271</v>
       </c>
@@ -8331,7 +8076,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
         <v>272</v>
       </c>
@@ -8339,7 +8084,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
         <v>273</v>
       </c>
@@ -8347,7 +8092,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
         <v>274</v>
       </c>
@@ -8355,7 +8100,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
         <v>276</v>
       </c>
@@ -8363,7 +8108,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
         <v>277</v>
       </c>
@@ -8371,7 +8116,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
         <v>278</v>
       </c>
@@ -8379,7 +8124,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="8" t="s">
         <v>279</v>
       </c>
@@ -8387,7 +8132,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
         <v>280</v>
       </c>
@@ -8395,7 +8140,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
         <v>281</v>
       </c>
@@ -8403,7 +8148,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
         <v>282</v>
       </c>
@@ -8411,7 +8156,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
         <v>283</v>
       </c>
@@ -8419,7 +8164,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
         <v>284</v>
       </c>
@@ -8427,7 +8172,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
         <v>285</v>
       </c>
@@ -8435,7 +8180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
         <v>286</v>
       </c>
@@ -8443,7 +8188,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" s="9" t="s">
         <v>287</v>
       </c>
@@ -8451,7 +8196,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" s="9" t="s">
         <v>288</v>
       </c>
@@ -8468,14 +8213,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B69"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="43.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="41.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="43.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8483,7 +8228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>293</v>
       </c>
@@ -8491,7 +8236,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>295</v>
       </c>
@@ -8499,7 +8244,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>296</v>
       </c>
@@ -8507,7 +8252,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>297</v>
       </c>
@@ -8515,7 +8260,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>298</v>
       </c>
@@ -8523,7 +8268,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>299</v>
       </c>
@@ -8531,7 +8276,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>300</v>
       </c>
@@ -8539,7 +8284,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>301</v>
       </c>
@@ -8547,7 +8292,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>302</v>
       </c>
@@ -8555,7 +8300,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>303</v>
       </c>
@@ -8563,7 +8308,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>304</v>
       </c>
@@ -8571,7 +8316,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>305</v>
       </c>
@@ -8579,7 +8324,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>306</v>
       </c>
@@ -8587,7 +8332,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>307</v>
       </c>
@@ -8595,7 +8340,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>308</v>
       </c>
@@ -8603,7 +8348,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>309</v>
       </c>
@@ -8611,7 +8356,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
         <v>310</v>
       </c>
@@ -8619,7 +8364,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="16" t="s">
         <v>311</v>
       </c>
@@ -8627,7 +8372,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="16" t="s">
         <v>312</v>
       </c>
@@ -8635,7 +8380,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="16" t="s">
         <v>313</v>
       </c>
@@ -8643,7 +8388,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="16" t="s">
         <v>314</v>
       </c>
@@ -8651,7 +8396,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="16" t="s">
         <v>315</v>
       </c>
@@ -8659,7 +8404,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="16" t="s">
         <v>316</v>
       </c>
@@ -8667,7 +8412,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="16" t="s">
         <v>317</v>
       </c>
@@ -8675,7 +8420,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>318</v>
       </c>
@@ -8683,7 +8428,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>320</v>
       </c>
@@ -8691,7 +8436,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>321</v>
       </c>
@@ -8699,7 +8444,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>322</v>
       </c>
@@ -8707,7 +8452,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>323</v>
       </c>
@@ -8715,7 +8460,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>324</v>
       </c>
@@ -8723,7 +8468,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>325</v>
       </c>
@@ -8731,7 +8476,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>326</v>
       </c>
@@ -8739,7 +8484,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>327</v>
       </c>
@@ -8747,7 +8492,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>328</v>
       </c>
@@ -8755,7 +8500,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>329</v>
       </c>
@@ -8763,7 +8508,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>330</v>
       </c>
@@ -8771,7 +8516,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>331</v>
       </c>
@@ -8779,7 +8524,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>332</v>
       </c>
@@ -8787,7 +8532,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="8" t="s">
         <v>334</v>
       </c>
@@ -8795,7 +8540,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="8" t="s">
         <v>335</v>
       </c>
@@ -8803,7 +8548,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
         <v>336</v>
       </c>
@@ -8811,7 +8556,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="8" t="s">
         <v>337</v>
       </c>
@@ -8819,7 +8564,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
         <v>338</v>
       </c>
@@ -8827,7 +8572,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>339</v>
       </c>
@@ -8835,7 +8580,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
         <v>340</v>
       </c>
@@ -8843,7 +8588,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>341</v>
       </c>
@@ -8851,7 +8596,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>342</v>
       </c>
@@ -8859,7 +8604,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
         <v>343</v>
       </c>
@@ -8867,7 +8612,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
         <v>344</v>
       </c>
@@ -8875,7 +8620,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
         <v>345</v>
       </c>
@@ -8883,7 +8628,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
         <v>347</v>
       </c>
@@ -8891,7 +8636,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
         <v>348</v>
       </c>
@@ -8899,7 +8644,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>349</v>
       </c>
@@ -8907,7 +8652,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>351</v>
       </c>
@@ -8915,7 +8660,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>352</v>
       </c>
@@ -8923,7 +8668,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>353</v>
       </c>
@@ -8931,7 +8676,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>354</v>
       </c>
@@ -8939,7 +8684,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>355</v>
       </c>
@@ -8947,7 +8692,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>356</v>
       </c>
@@ -8955,7 +8700,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>357</v>
       </c>
@@ -8963,7 +8708,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>358</v>
       </c>
@@ -8971,7 +8716,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>359</v>
       </c>
@@ -8979,7 +8724,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>360</v>
       </c>
@@ -8987,7 +8732,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>361</v>
       </c>
@@ -8995,7 +8740,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>362</v>
       </c>
@@ -9003,7 +8748,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>363</v>
       </c>
@@ -9011,7 +8756,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>364</v>
       </c>
@@ -9019,7 +8764,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>365</v>
       </c>
@@ -9037,15 +8782,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:P37"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="14" max="14" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="N2" s="3" t="s">
         <v>366</v>
       </c>
@@ -9056,13 +8801,13 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="20" t="s">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B3" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
       <c r="H3" s="28" t="s">
         <v>370</v>
       </c>
@@ -9079,10 +8824,10 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="23"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="24"/>
       <c r="H4" s="31"/>
       <c r="I4" s="32"/>
@@ -9098,7 +8843,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" s="25"/>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
@@ -9117,7 +8862,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.15">
       <c r="N6" s="1" t="s">
         <v>161</v>
       </c>
@@ -9128,7 +8873,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>381</v>
       </c>
@@ -9145,14 +8890,14 @@
         <v>384</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="20" t="s">
+    <row r="8" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B9" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
       <c r="H9" s="28" t="s">
         <v>386</v>
       </c>
@@ -9160,17 +8905,17 @@
       <c r="J9" s="29"/>
       <c r="K9" s="30"/>
     </row>
-    <row r="10" spans="2:16" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="23"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+    <row r="10" spans="2:16" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="24"/>
       <c r="H10" s="31"/>
       <c r="I10" s="32"/>
       <c r="J10" s="32"/>
       <c r="K10" s="33"/>
     </row>
-    <row r="11" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -9180,13 +8925,13 @@
       <c r="J11" s="35"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="2:16" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="37" t="s">
         <v>387</v>
       </c>
@@ -9197,13 +8942,13 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B14" s="37"/>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
       <c r="E14" s="37"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B15" s="37"/>
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
@@ -9215,31 +8960,31 @@
       <c r="J15" s="29"/>
       <c r="K15" s="30"/>
     </row>
-    <row r="16" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="33"/>
     </row>
-    <row r="17" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
+    <row r="17" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
       <c r="K17" s="36"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="23"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="24"/>
     </row>
-    <row r="19" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B19" s="25"/>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
@@ -9248,8 +8993,8 @@
         <v>391</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B21" t="s">
         <v>392</v>
       </c>
@@ -9260,31 +9005,31 @@
       <c r="J21" s="29"/>
       <c r="K21" s="30"/>
     </row>
-    <row r="22" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="H22" s="31"/>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="33"/>
     </row>
-    <row r="23" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="20" t="s">
+    <row r="23" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
       <c r="H23" s="34"/>
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
       <c r="K23" s="36"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="23"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="24"/>
     </row>
-    <row r="25" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B25" s="25"/>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
@@ -9293,62 +9038,62 @@
         <v>395</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="19" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B27" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="19" t="s">
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B31" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-    </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B35" s="20" t="s">
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+    </row>
+    <row r="34" spans="2:5" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B35" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B36" s="23"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="24"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -9356,11 +9101,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B3:E5"/>
-    <mergeCell ref="B9:E11"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="H9:K11"/>
-    <mergeCell ref="B27:E29"/>
     <mergeCell ref="B31:E33"/>
     <mergeCell ref="B35:E37"/>
     <mergeCell ref="H15:K17"/>
@@ -9368,6 +9108,11 @@
     <mergeCell ref="B13:E15"/>
     <mergeCell ref="B17:E19"/>
     <mergeCell ref="B23:E25"/>
+    <mergeCell ref="B3:E5"/>
+    <mergeCell ref="B9:E11"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="H9:K11"/>
+    <mergeCell ref="B27:E29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9378,19 +9123,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -9409,7 +9154,7 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -9428,7 +9173,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -9447,7 +9192,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -9466,7 +9211,7 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -9485,7 +9230,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -9504,7 +9249,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -9523,7 +9268,7 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -9542,7 +9287,7 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -9561,7 +9306,7 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -9580,7 +9325,7 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -9599,7 +9344,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -9618,7 +9363,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -9644,18 +9389,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9805,6 +9550,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{828852AD-0200-491F-83D2-C0A0FDC8BB33}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83F7A5DA-1B98-4A64-9D1E-26B3B73D80C1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -9816,14 +9569,6 @@
     <ds:schemaRef ds:uri="77d41baf-5ecc-4842-ba36-0ed33caf7049"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{828852AD-0200-491F-83D2-C0A0FDC8BB33}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/report_scripts/Brockway Paul/aggregation_mapping.xlsx
+++ b/report_scripts/Brockway Paul/aggregation_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkh2/github/PFUPipeline2/report_scripts/Brockway Paul/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leeds365-my.sharepoint.com/personal/earpebr_leeds_ac_uk/Documents/PFU 1960-2020 database research/InputData/v3.0a2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41476E5-6521-7D4A-AF0E-3E2BBB901F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="13_ncr:1_{11B3DC84-8A9C-0749-A7A0-D0517496FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4176347C-84C9-7D41-AA10-2FF56E52B037}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="16440" tabRatio="781" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="781" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="region_aggregation" sheetId="22" r:id="rId1"/>
@@ -59,7 +59,7 @@
     <author>Matthew Heun</author>
   </authors>
   <commentList>
-    <comment ref="A26" authorId="0" shapeId="0" xr:uid="{7F706F8C-8B21-E34D-BB5D-10AABAB85655}">
+    <comment ref="A176" authorId="0" shapeId="0" xr:uid="{7F706F8C-8B21-E34D-BB5D-10AABAB85655}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{3765D103-CCCE-A046-BEB9-6454192B8D2A}">
+    <comment ref="B176" authorId="0" shapeId="0" xr:uid="{3765D103-CCCE-A046-BEB9-6454192B8D2A}">
       <text>
         <r>
           <rPr>
@@ -125,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A27" authorId="0" shapeId="0" xr:uid="{F29CF95D-64E9-964F-B54D-209869AB0214}">
+    <comment ref="A177" authorId="0" shapeId="0" xr:uid="{F29CF95D-64E9-964F-B54D-209869AB0214}">
       <text>
         <r>
           <rPr>
@@ -158,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A28" authorId="0" shapeId="0" xr:uid="{B6D2A96F-C43E-3A4D-AFAA-2AECC04B8F0E}">
+    <comment ref="A387" authorId="0" shapeId="0" xr:uid="{B6D2A96F-C43E-3A4D-AFAA-2AECC04B8F0E}">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{28181293-E178-1445-AF91-D7C67E9514DF}">
+    <comment ref="B387" authorId="0" shapeId="0" xr:uid="{28181293-E178-1445-AF91-D7C67E9514DF}">
       <text>
         <r>
           <rPr>
@@ -224,7 +224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A29" authorId="0" shapeId="0" xr:uid="{061306E4-AEFF-704F-9284-1554D8154E7F}">
+    <comment ref="A388" authorId="0" shapeId="0" xr:uid="{061306E4-AEFF-704F-9284-1554D8154E7F}">
       <text>
         <r>
           <rPr>
@@ -257,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A30" authorId="1" shapeId="0" xr:uid="{F2EF713D-BA28-5641-BD2A-46DB13167D46}">
+    <comment ref="A389" authorId="1" shapeId="0" xr:uid="{F2EF713D-BA28-5641-BD2A-46DB13167D46}">
       <text>
         <r>
           <rPr>
@@ -490,7 +490,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="429">
   <si>
     <t>Many</t>
   </si>
@@ -1729,6 +1729,54 @@
   </si>
   <si>
     <t>OECD_KP</t>
+  </si>
+  <si>
+    <t>SRBXKX</t>
+  </si>
+  <si>
+    <t>Sub Saharan Africa_KP</t>
+  </si>
+  <si>
+    <t>Middle East and North Africa_KP</t>
+  </si>
+  <si>
+    <t>Eastern Europe_KP</t>
+  </si>
+  <si>
+    <t>South and South East Asia_KP</t>
+  </si>
+  <si>
+    <t>East Asia_KP</t>
+  </si>
+  <si>
+    <t>Western Europe_KP</t>
+  </si>
+  <si>
+    <t>Latin America_KP</t>
+  </si>
+  <si>
+    <t>Western offshoots_KP</t>
+  </si>
+  <si>
+    <t>HTH.1200.C</t>
+  </si>
+  <si>
+    <t>HTH.1800.C</t>
+  </si>
+  <si>
+    <t>LTH.90.C</t>
+  </si>
+  <si>
+    <t>MTH.120.C</t>
+  </si>
+  <si>
+    <t>MTH.130.C</t>
+  </si>
+  <si>
+    <t>MTH.150.C</t>
+  </si>
+  <si>
+    <t>MTH.160.C</t>
   </si>
 </sst>
 </file>
@@ -2385,6 +2433,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2395,9 +2446,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3311,11 +3359,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC20FE3-2C61-DD4B-AC4F-4EDDF1FDEE75}">
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B412"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" customWidth="1"/>
     <col min="3" max="16384" width="8.5" style="1"/>
   </cols>
   <sheetData>
@@ -3329,1311 +3377,1311 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>403</v>
+        <v>87</v>
+      </c>
+      <c r="B67" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>403</v>
+        <v>152</v>
+      </c>
+      <c r="B68" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>403</v>
+        <v>89</v>
+      </c>
+      <c r="B69" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>403</v>
+        <v>92</v>
+      </c>
+      <c r="B70" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>403</v>
+        <v>157</v>
+      </c>
+      <c r="B71" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>403</v>
+        <v>2</v>
+      </c>
+      <c r="B72" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>404</v>
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>404</v>
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>404</v>
+        <v>8</v>
+      </c>
+      <c r="B75" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>404</v>
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>404</v>
+        <v>16</v>
+      </c>
+      <c r="B77" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>404</v>
+        <v>17</v>
+      </c>
+      <c r="B78" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>404</v>
+        <v>19</v>
+      </c>
+      <c r="B79" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>404</v>
+        <v>139</v>
+      </c>
+      <c r="B80" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>404</v>
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>404</v>
+        <v>20</v>
+      </c>
+      <c r="B82" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>404</v>
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>404</v>
+        <v>40</v>
+      </c>
+      <c r="B84" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>404</v>
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>404</v>
+        <v>6</v>
+      </c>
+      <c r="B86" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>404</v>
+        <v>22</v>
+      </c>
+      <c r="B87" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>404</v>
+        <v>45</v>
+      </c>
+      <c r="B88" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>404</v>
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>404</v>
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>404</v>
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>404</v>
+        <v>23</v>
+      </c>
+      <c r="B92" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>404</v>
+        <v>24</v>
+      </c>
+      <c r="B93" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>405</v>
+        <v>51</v>
+      </c>
+      <c r="B94" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>405</v>
+        <v>53</v>
+      </c>
+      <c r="B95" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>406</v>
+        <v>13</v>
+      </c>
+      <c r="B96" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>406</v>
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>406</v>
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>406</v>
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>406</v>
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>406</v>
+        <v>18</v>
+      </c>
+      <c r="B101" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>406</v>
+        <v>163</v>
+      </c>
+      <c r="B102" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>406</v>
+        <v>26</v>
+      </c>
+      <c r="B103" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>406</v>
+        <v>26</v>
+      </c>
+      <c r="B104" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>406</v>
+        <v>14</v>
+      </c>
+      <c r="B105" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A160" s="1" t="s">
-        <v>134</v>
+      <c r="A160" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>409</v>
@@ -4641,15 +4689,15 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A167" s="1" t="s">
-        <v>5</v>
+      <c r="A167" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>409</v>
@@ -4657,7 +4705,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>409</v>
@@ -4665,7 +4713,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>409</v>
@@ -4673,7 +4721,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>409</v>
@@ -4681,7 +4729,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>409</v>
@@ -4689,7 +4737,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>409</v>
@@ -4697,7 +4745,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>409</v>
@@ -4705,15 +4753,15 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A175" s="1" t="s">
-        <v>6</v>
+      <c r="A175" s="18" t="s">
+        <v>163</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>409</v>
@@ -4721,74 +4769,74 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>409</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.15">
@@ -4796,111 +4844,111 @@
         <v>10</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A190" s="18" t="s">
-        <v>24</v>
+      <c r="A190" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>409</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A197" s="18" t="s">
-        <v>25</v>
+      <c r="A197" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.15">
@@ -4908,498 +4956,1717 @@
         <v>15</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>409</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A205" s="18" t="s">
-        <v>163</v>
+      <c r="A205" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>410</v>
+        <v>35</v>
+      </c>
+      <c r="B209" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>410</v>
+        <v>56</v>
+      </c>
+      <c r="B210" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>410</v>
+        <v>58</v>
+      </c>
+      <c r="B211" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>410</v>
+        <v>57</v>
+      </c>
+      <c r="B212" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>410</v>
+        <v>69</v>
+      </c>
+      <c r="B213" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>410</v>
+        <v>70</v>
+      </c>
+      <c r="B214" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>410</v>
+        <v>71</v>
+      </c>
+      <c r="B215" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>411</v>
+        <v>72</v>
+      </c>
+      <c r="B216" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>411</v>
+        <v>170</v>
+      </c>
+      <c r="B217" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>411</v>
+        <v>73</v>
+      </c>
+      <c r="B218" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>411</v>
+        <v>75</v>
+      </c>
+      <c r="B219" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>411</v>
+        <v>76</v>
+      </c>
+      <c r="B220" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>411</v>
+        <v>78</v>
+      </c>
+      <c r="B221" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>411</v>
+        <v>77</v>
+      </c>
+      <c r="B222" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>412</v>
+        <v>79</v>
+      </c>
+      <c r="B223" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>412</v>
+        <v>80</v>
+      </c>
+      <c r="B224" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>412</v>
+        <v>171</v>
+      </c>
+      <c r="B225" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>412</v>
+        <v>81</v>
+      </c>
+      <c r="B226" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>412</v>
+        <v>82</v>
+      </c>
+      <c r="B227" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>412</v>
+        <v>59</v>
+      </c>
+      <c r="B228" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>412</v>
+        <v>74</v>
+      </c>
+      <c r="B229" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>412</v>
+        <v>172</v>
+      </c>
+      <c r="B230" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A231" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>412</v>
+        <v>83</v>
+      </c>
+      <c r="B231" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A232" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>412</v>
+        <v>60</v>
+      </c>
+      <c r="B232" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A233" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>412</v>
+        <v>173</v>
+      </c>
+      <c r="B233" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A234" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A235" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A236" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A237" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A238" s="1" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A239" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>412</v>
+        <v>108</v>
+      </c>
+      <c r="B239" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A240" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>412</v>
+        <v>115</v>
+      </c>
+      <c r="B240" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A241" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>412</v>
+        <v>121</v>
+      </c>
+      <c r="B241" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A242" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>412</v>
+        <v>124</v>
+      </c>
+      <c r="B242" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A243" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>412</v>
+        <v>135</v>
+      </c>
+      <c r="B243" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A244" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>412</v>
+        <v>94</v>
+      </c>
+      <c r="B244" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A245" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>412</v>
+        <v>107</v>
+      </c>
+      <c r="B245" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A246" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>412</v>
+        <v>96</v>
+      </c>
+      <c r="B246" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>412</v>
+        <v>97</v>
+      </c>
+      <c r="B247" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>412</v>
+        <v>98</v>
+      </c>
+      <c r="B248" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>412</v>
+        <v>99</v>
+      </c>
+      <c r="B249" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>412</v>
+        <v>100</v>
+      </c>
+      <c r="B250" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>412</v>
+        <v>101</v>
+      </c>
+      <c r="B251" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>412</v>
+        <v>102</v>
+      </c>
+      <c r="B252" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>412</v>
+        <v>103</v>
+      </c>
+      <c r="B253" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>412</v>
+        <v>104</v>
+      </c>
+      <c r="B254" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>412</v>
+        <v>105</v>
+      </c>
+      <c r="B255" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>412</v>
+        <v>106</v>
+      </c>
+      <c r="B256" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A258" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A261" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A262" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A263" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A264" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A265" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A266" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A267" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A268" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A269" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A270" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A271" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A272" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A273" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A274" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A275" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A276" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A277" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A278" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A279" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A280" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A281" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A282" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A283" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A284" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A285" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A286" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A287" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A288" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A289" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A290" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A291" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A292" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A293" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A294" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A295" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A296" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A297" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A298" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A299" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A300" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A301" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A302" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A303" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A304" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A305" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A306" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A307" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A308" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="B308" s="1" t="s">
         <v>412</v>
       </c>
     </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A309" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A310" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A311" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A312" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A313" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A314" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A315" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A316" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A317" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A318" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A319" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A320" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A321" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A322" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A323" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A324" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A325" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A326" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A327" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A328" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A329" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A330" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A331" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A332" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A333" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A334" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A335" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A336" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A337" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A338" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A339" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A340" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B340" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A341" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B341" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A342" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B342" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A343" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B343" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A344" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B344" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A345" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B345" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A346" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B346" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A347" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B347" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A348" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B348" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A349" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B349" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A350" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B350" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A351" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B351" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A352" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B352" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A353" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B353" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A354" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B354" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A355" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B355" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A356" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A357" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A358" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B358" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A359" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B359" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A360" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B360" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A361" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B361" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A362" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B362" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A363" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B363" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A364" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B364" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A365" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B365" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A366" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B366" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A367" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B367" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A368" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B368" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A369" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B369" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A370" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B370" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A371" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B371" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A372" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B372" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A373" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B373" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A374" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B374" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A375" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B375" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A376" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B376" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A377" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B377" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A378" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B378" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A379" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B379" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A380" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B380" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A381" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B381" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A382" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B382" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A383" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B383" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A384" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B384" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A385" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B385" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A386" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B386" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A387" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A388" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A389" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A390" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B390" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A391" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B391" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A392" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B392" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A393" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B393" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A394" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B394" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A395" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B395" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A396" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B396" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A397" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B397" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A398" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B398" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A399" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B399" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A400" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B400" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A401" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B401" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A402" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B402" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A403" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B403" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A404" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B404" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A405" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B405" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A406" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B406" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A407" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B407" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A408" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B408" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A409" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B409" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A410" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B410" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A411" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B411" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A412" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B412" t="s">
+        <v>421</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B412">
+    <sortCondition ref="B2:B412"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -6793,7 +8060,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.5" style="14" bestFit="1" customWidth="1"/>
@@ -6843,7 +8110,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>182</v>
@@ -6851,7 +8118,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>182</v>
@@ -6859,7 +8126,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>182</v>
@@ -6867,7 +8134,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>182</v>
@@ -6875,7 +8142,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>182</v>
@@ -6883,7 +8150,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="15" t="s">
-        <v>187</v>
+        <v>422</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>182</v>
@@ -6891,7 +8158,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>182</v>
@@ -6899,55 +8166,55 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
-        <v>190</v>
+        <v>423</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" s="15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>195</v>
@@ -6955,31 +8222,31 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
-        <v>201</v>
+        <v>424</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>199</v>
@@ -6987,75 +8254,386 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" s="15" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" s="15" t="s">
-        <v>208</v>
+        <v>425</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" s="15" t="s">
-        <v>209</v>
+        <v>426</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
-        <v>210</v>
+        <v>427</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
-        <v>211</v>
+        <v>428</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A33" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A34" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A35" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A36" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A37" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A38" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A39" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B39" s="15" t="s">
         <v>212</v>
       </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B40" s="14"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B41" s="14"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B42" s="14"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B43" s="14"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B44" s="14"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B45" s="14"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B46" s="14"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B47" s="14"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B48" s="14"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B49" s="14"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B50" s="14"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B51" s="14"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B52" s="14"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B53" s="14"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B54" s="14"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B55" s="14"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B56" s="14"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B57" s="14"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B58" s="14"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B59" s="14"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B60" s="14"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B61" s="14"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B62" s="14"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B63" s="14"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B64" s="14"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B65" s="14"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B66" s="14"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B67" s="14"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B68" s="14"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B69" s="14"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B70" s="14"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B71" s="14"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B72" s="14"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B73" s="14"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B74" s="14"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B75" s="14"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B76" s="14"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B77" s="14"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B78" s="14"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B79" s="14"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B80" s="14"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B81" s="14"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B82" s="14"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B83" s="14"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B84" s="14"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B85" s="14"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B86" s="14"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B87" s="14"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B88" s="14"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B89" s="14"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B90" s="14"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B91" s="14"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B92" s="14"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B93" s="14"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B94" s="14"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B95" s="14"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B96" s="14"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B97" s="14"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B98" s="14"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B99" s="14"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B100" s="14"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B101" s="14"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B102" s="14"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B103" s="14"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B104" s="14"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B105" s="14"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B106" s="14"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B107" s="14"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B108" s="14"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B109" s="14"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B110" s="14"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B111" s="14"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B112" s="14"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B113" s="14"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B114" s="14"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B115" s="14"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B116" s="14"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B117" s="14"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B118" s="14"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B119" s="14"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B120" s="14"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B121" s="14"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B122" s="14"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B123" s="14"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B124" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
@@ -8802,12 +10380,12 @@
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
       <c r="H3" s="28" t="s">
         <v>370</v>
       </c>
@@ -8825,9 +10403,9 @@
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
       <c r="E4" s="24"/>
       <c r="H4" s="31"/>
       <c r="I4" s="32"/>
@@ -8892,12 +10470,12 @@
     </row>
     <row r="8" spans="2:16" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
       <c r="H9" s="28" t="s">
         <v>386</v>
       </c>
@@ -8906,9 +10484,9 @@
       <c r="K9" s="30"/>
     </row>
     <row r="10" spans="2:16" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="24"/>
       <c r="H10" s="31"/>
       <c r="I10" s="32"/>
@@ -8967,21 +10545,21 @@
       <c r="K16" s="33"/>
     </row>
     <row r="17" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
       <c r="H17" s="34"/>
       <c r="I17" s="35"/>
       <c r="J17" s="35"/>
       <c r="K17" s="36"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
       <c r="E18" s="24"/>
     </row>
     <row r="19" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -9012,21 +10590,21 @@
       <c r="K22" s="33"/>
     </row>
     <row r="23" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
       <c r="H23" s="34"/>
       <c r="I23" s="35"/>
       <c r="J23" s="35"/>
       <c r="K23" s="36"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
       <c r="E24" s="24"/>
     </row>
     <row r="25" spans="2:11" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -9039,58 +10617,58 @@
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="2:5" ht="14" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="35" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="24"/>
     </row>
     <row r="37" spans="2:5" ht="14" thickBot="1" x14ac:dyDescent="0.2">
@@ -9101,6 +10679,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:E5"/>
+    <mergeCell ref="B9:E11"/>
+    <mergeCell ref="H3:K5"/>
+    <mergeCell ref="H9:K11"/>
+    <mergeCell ref="B27:E29"/>
     <mergeCell ref="B31:E33"/>
     <mergeCell ref="B35:E37"/>
     <mergeCell ref="H15:K17"/>
@@ -9108,11 +10691,6 @@
     <mergeCell ref="B13:E15"/>
     <mergeCell ref="B17:E19"/>
     <mergeCell ref="B23:E25"/>
-    <mergeCell ref="B3:E5"/>
-    <mergeCell ref="B9:E11"/>
-    <mergeCell ref="H3:K5"/>
-    <mergeCell ref="H9:K11"/>
-    <mergeCell ref="B27:E29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9389,18 +10967,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9550,25 +11128,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{828852AD-0200-491F-83D2-C0A0FDC8BB33}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83F7A5DA-1B98-4A64-9D1E-26B3B73D80C1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="77d41baf-5ecc-4842-ba36-0ed33caf7049"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83F7A5DA-1B98-4A64-9D1E-26B3B73D80C1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{828852AD-0200-491F-83D2-C0A0FDC8BB33}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="77d41baf-5ecc-4842-ba36-0ed33caf7049"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
